--- a/artfynd/A 25265-2024 artfynd.xlsx
+++ b/artfynd/A 25265-2024 artfynd.xlsx
@@ -900,11 +900,11 @@
         <v>117071916</v>
       </c>
       <c r="B4" t="n">
-        <v>56494</v>
+        <v>56532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 25265-2024 artfynd.xlsx
+++ b/artfynd/A 25265-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114940099</v>
+        <v>121667759</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
+        <v>97064</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>6648803</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 25265-2024 artfynd.xlsx
+++ b/artfynd/A 25265-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121667759</v>
       </c>
       <c r="B2" t="n">
-        <v>97064</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25265-2024 artfynd.xlsx
+++ b/artfynd/A 25265-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>117071916</v>
       </c>
       <c r="B4" t="n">
-        <v>56560</v>
+        <v>56569</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 25265-2024 artfynd.xlsx
+++ b/artfynd/A 25265-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121667759</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>97085</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>117071916</v>
       </c>
       <c r="B4" t="n">
-        <v>56569</v>
+        <v>56577</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 25265-2024 artfynd.xlsx
+++ b/artfynd/A 25265-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121667759</v>
       </c>
       <c r="B2" t="n">
-        <v>97085</v>
+        <v>97087</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25265-2024 artfynd.xlsx
+++ b/artfynd/A 25265-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121667759</v>
       </c>
       <c r="B2" t="n">
-        <v>97087</v>
+        <v>97094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25265-2024 artfynd.xlsx
+++ b/artfynd/A 25265-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>117071916</v>
       </c>
       <c r="B4" t="n">
-        <v>56577</v>
+        <v>56581</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 25265-2024 artfynd.xlsx
+++ b/artfynd/A 25265-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>117071916</v>
       </c>
       <c r="B4" t="n">
-        <v>56581</v>
+        <v>56582</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 25265-2024 artfynd.xlsx
+++ b/artfynd/A 25265-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>117071916</v>
       </c>
       <c r="B4" t="n">
-        <v>56582</v>
+        <v>56584</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 25265-2024 artfynd.xlsx
+++ b/artfynd/A 25265-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>117071916</v>
       </c>
       <c r="B4" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
